--- a/Excel 3/Planilha 0.xlsx
+++ b/Excel 3/Planilha 0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno\Documents\GitHub\Ezequiel\Excel 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DCFD652-0358-472C-86F8-DCD06B04388C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49CE48E-E454-4F3E-B28D-40186EE603EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="8100" windowWidth="14610" windowHeight="8205" xr2:uid="{6412FD18-E83E-42DF-ACEB-57EDC3AE2E08}"/>
+    <workbookView xWindow="3810" yWindow="3810" windowWidth="21600" windowHeight="11835" xr2:uid="{6412FD18-E83E-42DF-ACEB-57EDC3AE2E08}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -139,12 +139,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -156,13 +159,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -489,15 +486,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="5"/>
-      <c r="E1" s="6" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="6"/>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="7">
+      <c r="F1" s="3">
         <v>5</v>
       </c>
     </row>
@@ -516,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1">
-        <f>E2*F1</f>
+        <f>E2*F$1</f>
         <v>5</v>
       </c>
     </row>
@@ -535,7 +532,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="1">
-        <f>E3*F1</f>
+        <f t="shared" ref="F3:F11" si="1">E3*F$1</f>
         <v>10</v>
       </c>
     </row>
@@ -554,7 +551,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="1">
-        <f>E4*F1</f>
+        <f>E4*F$1</f>
         <v>15</v>
       </c>
     </row>
@@ -573,7 +570,7 @@
         <v>4</v>
       </c>
       <c r="F5" s="1">
-        <f>E5*F1</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
     </row>
@@ -592,7 +589,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="1">
-        <f>E6*F1</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
     </row>
@@ -611,7 +608,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="1">
-        <f>E7*F1</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
@@ -630,7 +627,7 @@
         <v>7</v>
       </c>
       <c r="F8" s="1">
-        <f>E8*F1</f>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
     </row>
@@ -649,7 +646,7 @@
         <v>8</v>
       </c>
       <c r="F9" s="1">
-        <f>E9*F1</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
     </row>
@@ -668,7 +665,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="1">
-        <f>E10*F1</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
     </row>
@@ -687,20 +684,20 @@
         <v>10</v>
       </c>
       <c r="F11" s="1">
-        <f>E11*F2</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="E12" s="8" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="E12" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="8"/>
+      <c r="F12" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Excel 3/Planilha 0.xlsx
+++ b/Excel 3/Planilha 0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno\Documents\GitHub\Ezequiel\Excel 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49CE48E-E454-4F3E-B28D-40186EE603EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20E0805-43F5-49B7-9F34-5BFD33C08D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3810" yWindow="3810" windowWidth="21600" windowHeight="11835" xr2:uid="{6412FD18-E83E-42DF-ACEB-57EDC3AE2E08}"/>
   </bookViews>
@@ -684,7 +684,7 @@
         <v>10</v>
       </c>
       <c r="F11" s="1">
-        <f t="shared" si="1"/>
+        <f>E11*F$1</f>
         <v>50</v>
       </c>
     </row>
